--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484220_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484220_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.839700000000001</v>
+        <v>9.491300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4081</v>
+        <v>7.2776</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4316</v>
+        <v>2.2137</v>
       </c>
       <c r="G2" t="n">
         <v>8.9095</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2976</v>
+        <v>0.9492</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8941</v>
+        <v>-0.0246</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1917</v>
+        <v>0.9738</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0277</v>
+        <v>3.9682</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0799</v>
+        <v>2.1292</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9479</v>
+        <v>1.8389</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0527</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1037</v>
+        <v>1.0441</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4171</v>
+        <v>0.4664</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6866</v>
+        <v>0.5777</v>
       </c>
       <c r="V3" t="n">
         <v>1.2186</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3698</v>
+        <v>3.4732</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5447</v>
+        <v>4.403</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.175</v>
+        <v>-0.9298</v>
       </c>
       <c r="G4" t="n">
         <v>1.0613</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1718</v>
+        <v>0.2752</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6219</v>
+        <v>0.4802</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V4" t="n">
         <v>1.5507</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9431</v>
+        <v>2.6789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2349</v>
+        <v>1.421</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7082</v>
+        <v>1.258</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3068</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3543</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6611</v>
+        <v>0.3371</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0123</v>
+        <v>1.5007</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0526</v>
+        <v>0.7585</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0649</v>
+        <v>0.7422</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2945</v>
+        <v>-0.5496</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6984</v>
+        <v>-0.1445</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4039</v>
+        <v>-0.4051</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6406</v>
+        <v>0.3604</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9234</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7172</v>
+        <v>0.4401</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6284</v>
+        <v>2.5739</v>
       </c>
       <c r="E6" t="n">
         <v>2.4555</v>
       </c>
       <c r="F6" t="n">
-        <v>0.173</v>
+        <v>0.1185</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2237</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6102</v>
+        <v>0.5558</v>
       </c>
       <c r="T6" t="n">
         <v>0.1899</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4203</v>
+        <v>0.3658</v>
       </c>
       <c r="V6" t="n">
         <v>2.4373</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1111</v>
+        <v>2.5701</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0165</v>
+        <v>1.5239</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0946</v>
+        <v>1.0463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9510999999999999</v>
+        <v>2.63</v>
       </c>
       <c r="H7" t="n">
-        <v>0.614</v>
+        <v>-0.3502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3371</v>
+        <v>2.9803</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5007</v>
+        <v>3.1243</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7585</v>
+        <v>0.4131</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7422</v>
+        <v>2.7112</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5496</v>
+        <v>-0.4943</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1445</v>
+        <v>-0.7634</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>0.269</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2074</v>
+        <v>0.8034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4842</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2767</v>
+        <v>0.7276</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6639</v>
+        <v>1.3406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9172</v>
+        <v>-0.8774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7467</v>
+        <v>2.2179</v>
       </c>
       <c r="G8" t="n">
-        <v>2.63</v>
+        <v>-0.3068</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3502</v>
+        <v>0.3543</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9803</v>
+        <v>-0.6611</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1243</v>
+        <v>-0.0123</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4131</v>
+        <v>1.0526</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7112</v>
+        <v>-1.0649</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4943</v>
+        <v>-0.2945</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7634</v>
+        <v>-0.6984</v>
       </c>
       <c r="O8" t="n">
-        <v>0.269</v>
+        <v>0.4039</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1029</v>
+        <v>2.0381</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5309</v>
+        <v>0.8111</v>
       </c>
       <c r="U8" t="n">
-        <v>0.428</v>
+        <v>1.2269</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1115</v>
+        <v>0.8548</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0271</v>
+        <v>0.8248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0712</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0422</v>
+        <v>0.7855</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5752</v>
+        <v>0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4671</v>
+        <v>0.4126</v>
       </c>
       <c r="V9" t="n">
         <v>0.5545</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.302</v>
+        <v>-0.2066</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1436</v>
+        <v>-0.275</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4456</v>
+        <v>0.0684</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4043</v>
+        <v>-0.6365</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.1241</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1326</v>
+        <v>-0.5124</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0747</v>
+        <v>0.4574</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6536</v>
+        <v>0.4298</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7284</v>
+        <v>0.0276</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3296</v>
+        <v>-1.0939</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0747</v>
+        <v>-0.5538</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4043</v>
+        <v>-0.5401</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0737</v>
+        <v>0.4299</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0689</v>
+        <v>0.2443</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1425</v>
+        <v>0.1856</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3393</v>
+        <v>-0.2124</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1044</v>
+        <v>0.0425</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4436</v>
+        <v>-0.2549</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9791</v>
+        <v>0.4043</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3976</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4185</v>
+        <v>1.1326</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3243</v>
+        <v>0.0747</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3646</v>
+        <v>-0.6536</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6889</v>
+        <v>0.7284</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3034</v>
+        <v>0.3296</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.033</v>
+        <v>-0.0747</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2704</v>
+        <v>0.4043</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9757</v>
+        <v>0.0159</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7567</v>
+        <v>-0.0322</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2189</v>
+        <v>0.0481</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4408</v>
+        <v>-0.3142</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.42</v>
+        <v>-2.1572</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9792</v>
+        <v>1.843</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5688</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.542</v>
+        <v>0.6686</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2337</v>
+        <v>0.029</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3133</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2456</v>
+        <v>-0.199</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0677</v>
+        <v>-0.4164</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6365</v>
+        <v>-0.9791</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1241</v>
+        <v>-1.3976</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5124</v>
+        <v>0.4185</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4574</v>
+        <v>0.3243</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4298</v>
+        <v>-0.3646</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0276</v>
+        <v>0.6889</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0939</v>
+        <v>-1.3034</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5538</v>
+        <v>-1.033</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6768</v>
+        <v>0.6996</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.4534</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0495</v>
+        <v>0.2462</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.2998</v>
+        <v>25.6024</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2663</v>
+        <v>16.5689</v>
       </c>
       <c r="F14" t="n">
-        <v>9.033799999999999</v>
+        <v>9.0336</v>
       </c>
       <c r="G14" t="n">
-        <v>9.1174</v>
+        <v>9.117399999999998</v>
       </c>
       <c r="H14" t="n">
         <v>-7.0658</v>
@@ -1522,7 +1522,7 @@
         <v>17.4561</v>
       </c>
       <c r="K14" t="n">
-        <v>2.614200000000001</v>
+        <v>2.6142</v>
       </c>
       <c r="L14" t="n">
         <v>14.8421</v>
@@ -1546,10 +1546,10 @@
         <v>13.6738</v>
       </c>
       <c r="S14" t="n">
-        <v>8.323</v>
+        <v>8.6257</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6839</v>
+        <v>2.9865</v>
       </c>
       <c r="U14" t="n">
         <v>5.638999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4595</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>4.4222</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9628</v>
+        <v>-4.3454</v>
       </c>
       <c r="G15" t="n">
         <v>2.512</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6505</v>
+        <v>-1.0332</v>
       </c>
       <c r="T15" t="n">
         <v>-0.8995</v>
       </c>
       <c r="U15" t="n">
-        <v>0.249</v>
+        <v>-0.1337</v>
       </c>
       <c r="V15" t="n">
         <v>-2.7693</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3966</v>
+        <v>-0.2138</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2369</v>
+        <v>-0.1358</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1597</v>
+        <v>-0.078</v>
       </c>
       <c r="G16" t="n">
         <v>0.7072000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3224</v>
+        <v>-0.1396</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5576</v>
+        <v>-0.7871</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8139</v>
+        <v>-1.0161</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2563</v>
+        <v>0.2291</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1255</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1772</v>
+        <v>-0.0523</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3715</v>
+        <v>0.1693</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1943</v>
+        <v>-0.2215</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6634</v>
+        <v>-1.5544</v>
       </c>
       <c r="E18" t="n">
         <v>-1.7172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0538</v>
+        <v>0.1627</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6382</v>
@@ -1858,13 +1858,13 @@
         <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4391</v>
+        <v>-0.3302</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1073</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3318</v>
+        <v>-0.2229</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7297</v>
+        <v>-1.6568</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7297</v>
+        <v>-1.5543</v>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>-0.1025</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7139</v>
+        <v>-2.229</v>
       </c>
       <c r="H19" t="n">
-        <v>0.768</v>
+        <v>-1.2845</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0541</v>
+        <v>-0.9445</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0633</v>
+        <v>-1.2049</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9824000000000001</v>
+        <v>-1.2049</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>-1.0241</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.0795</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.9445</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.4045</v>
+      </c>
+      <c r="T19" t="n">
         <v>-0.3494</v>
       </c>
-      <c r="N19" t="n">
-        <v>-0.2144</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.135</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.7814</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.1953</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.7208</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.4842</v>
-      </c>
       <c r="U19" t="n">
-        <v>-0.2367</v>
+        <v>-0.0551</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9005</v>
+        <v>-1.7297</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5543</v>
+        <v>-0.7297</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3462</v>
+        <v>-1</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.229</v>
+        <v>0.7139</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2845</v>
+        <v>0.768</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9445</v>
+        <v>-0.0541</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2049</v>
+        <v>1.0633</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2049</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0241</v>
+        <v>-0.3494</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0795</v>
+        <v>-0.2144</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9445</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6482</v>
+        <v>-0.7208</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3494</v>
+        <v>-0.4842</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2989</v>
+        <v>-0.2367</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9496</v>
+        <v>-1.8369</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1529</v>
+        <v>-0.8496</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7966</v>
+        <v>-0.9873</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2475</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4518</v>
+        <v>-0.3391</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="U21" t="n">
-        <v>0.335</v>
+        <v>0.1443</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0549</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9625</v>
+        <v>-2.1531</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9258999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0366</v>
+        <v>-1.2272</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1337</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8287</v>
+        <v>-1.0194</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6657</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.163</v>
+        <v>-0.3536</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1529</v>
+        <v>-3.1113</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1461</v>
+        <v>-1.3483</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0067</v>
+        <v>-1.763</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2391</v>
@@ -2248,13 +2248,13 @@
         <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1557</v>
+        <v>-0.1142</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0083</v>
+        <v>-0.1939</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.164</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3342</v>
+        <v>-3.5358</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1432</v>
+        <v>-1.4771</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.191</v>
+        <v>-2.0587</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4444</v>
+        <v>0.193</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0893</v>
+        <v>2.2415</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.5337</v>
+        <v>-2.0486</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1766</v>
+        <v>3.5445</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7421</v>
+        <v>2.6247</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5655</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.621</v>
+        <v>-3.3516</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6528</v>
+        <v>-0.3832</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.9682</v>
+        <v>-2.9684</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4172</v>
+        <v>-1.7753</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-1.1148</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2264</v>
+        <v>-0.6605</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3372</v>
+        <v>-3.7012</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.053</v>
+        <v>-1.3455</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2841</v>
+        <v>-2.3557</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.186</v>
+        <v>-2.4444</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0824</v>
+        <v>1.0893</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1036</v>
+        <v>-3.5337</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7429</v>
+        <v>1.1766</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.449</v>
+        <v>1.7421</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2939</v>
+        <v>-0.5655</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4431</v>
+        <v>-3.621</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6334</v>
+        <v>-0.6528</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8097</v>
+        <v>-2.9682</v>
       </c>
       <c r="P25" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8507</v>
+        <v>-0.7842</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.22</v>
+        <v>-0.8459</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6307</v>
+        <v>0.0617</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7731</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7753</v>
+        <v>-4.4226</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9826</v>
+        <v>-2.3564</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7927</v>
+        <v>-2.0663</v>
       </c>
       <c r="G26" t="n">
-        <v>0.193</v>
+        <v>-3.186</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2415</v>
+        <v>-1.0824</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0486</v>
+        <v>-2.1036</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5445</v>
+        <v>-1.7429</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6247</v>
+        <v>-0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9199000000000001</v>
+        <v>-1.2939</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.3516</v>
+        <v>-1.4431</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3832</v>
+        <v>-0.6334</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.9684</v>
+        <v>-0.8097</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.0149</v>
+        <v>-0.9361</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6203</v>
+        <v>-0.5233</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3945</v>
+        <v>-0.4128</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-25.3</v>
+        <v>-24.6259</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.0335</v>
+        <v>-9.0337</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.2663</v>
+        <v>-15.5923</v>
       </c>
       <c r="G27" t="n">
         <v>-9.1173</v>
@@ -2536,7 +2536,7 @@
         <v>8.338800000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>9.680099999999999</v>
+        <v>9.680100000000001</v>
       </c>
       <c r="L27" t="n">
         <v>-1.3412</v>
@@ -2560,13 +2560,13 @@
         <v>10.7437</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.322800000000001</v>
+        <v>-7.648899999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.6391</v>
+        <v>-5.639200000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.6838</v>
+        <v>-2.0097</v>
       </c>
       <c r="V27" t="n">
         <v>-4.9293</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484220_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484220_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6789</v>
+        <v>2.5739</v>
       </c>
       <c r="E5" t="n">
-        <v>1.421</v>
+        <v>2.4555</v>
       </c>
       <c r="F5" t="n">
-        <v>1.258</v>
+        <v>0.1185</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.2237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.614</v>
+        <v>-1.3832</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3371</v>
+        <v>1.1595</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5007</v>
+        <v>0.805</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7585</v>
+        <v>-0.4899</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7422</v>
+        <v>1.2949</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5496</v>
+        <v>-1.0287</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1445</v>
+        <v>-0.8933</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4051</v>
+        <v>-0.1354</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3604</v>
+        <v>0.5558</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.1899</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4401</v>
+        <v>0.3658</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5739</v>
+        <v>2.5701</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4555</v>
+        <v>1.5239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1185</v>
+        <v>1.0463</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2237</v>
+        <v>2.63</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3832</v>
+        <v>-0.3502</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1595</v>
+        <v>2.9803</v>
       </c>
       <c r="J6" t="n">
-        <v>0.805</v>
+        <v>3.1243</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4899</v>
+        <v>0.4131</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2949</v>
+        <v>2.7112</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0287</v>
+        <v>-0.4943</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8933</v>
+        <v>-0.7634</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1354</v>
+        <v>0.269</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5558</v>
+        <v>0.8034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1899</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3658</v>
+        <v>0.7276</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4373</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5701</v>
+        <v>1.521</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5239</v>
+        <v>1.521</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0463</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.63</v>
+        <v>1.521</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3502</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9803</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1243</v>
+        <v>1.521</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4131</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7112</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4943</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7634</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8034</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07580000000000001</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7276</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3406</v>
+        <v>1.158</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8774</v>
+        <v>-0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2179</v>
+        <v>1.258</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3068</v>
+        <v>-0.5698</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3543</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6611</v>
+        <v>-0.8768</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0123</v>
+        <v>-0.0203</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0526</v>
+        <v>0.4515</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0649</v>
+        <v>-0.4718</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2945</v>
+        <v>-0.5496</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6984</v>
+        <v>-0.1445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4039</v>
+        <v>-0.4051</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0381</v>
+        <v>0.3604</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8111</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2269</v>
+        <v>0.4401</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8548</v>
+        <v>1.0336</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8248</v>
+        <v>-1.1844</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03</v>
+        <v>2.2179</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0712</v>
+        <v>-0.6138</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4482</v>
+        <v>0.0473</v>
       </c>
       <c r="I9" t="n">
-        <v>0.377</v>
+        <v>-0.6611</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1026</v>
+        <v>-0.3193</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3454</v>
+        <v>0.7457</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>-1.0649</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9686</v>
+        <v>-0.2945</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1028</v>
+        <v>-0.6984</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1342</v>
+        <v>0.4039</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7855</v>
+        <v>2.0381</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3729</v>
+        <v>0.8111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4126</v>
+        <v>1.2269</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1234,72 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2066</v>
+        <v>0.8548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.275</v>
+        <v>0.8248</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0684</v>
+        <v>0.03</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6365</v>
+        <v>-1.0712</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1241</v>
+        <v>-1.4482</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5124</v>
+        <v>0.377</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4574</v>
+        <v>-0.1026</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4298</v>
+        <v>-0.3454</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0276</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0939</v>
+        <v>-0.9686</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5538</v>
+        <v>-1.1028</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5401</v>
+        <v>0.1342</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4299</v>
+        <v>0.7855</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2443</v>
+        <v>0.3729</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1856</v>
+        <v>0.4126</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2124</v>
+        <v>0.607</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0425</v>
+        <v>0.607</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2549</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4043</v>
+        <v>0.607</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1326</v>
+        <v>0.607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0747</v>
+        <v>0.607</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6536</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3296</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0322</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0481</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3142</v>
+        <v>0.307</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1572</v>
+        <v>0.307</v>
       </c>
       <c r="F12" t="n">
-        <v>1.843</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5688</v>
+        <v>0.307</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4879</v>
+        <v>0.307</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0809</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2095</v>
+        <v>0.307</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5897</v>
+        <v>0.307</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6198</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3593</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8982</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5389</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6686</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6395999999999999</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1406,12 +1461,17 @@
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.2066</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.199</v>
+        <v>-0.275</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4164</v>
+        <v>0.0684</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9791</v>
+        <v>-0.6365</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3976</v>
+        <v>-0.1241</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4185</v>
+        <v>-0.5124</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3243</v>
+        <v>0.4574</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3646</v>
+        <v>0.4298</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6889</v>
+        <v>0.0276</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3034</v>
+        <v>-1.0939</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.033</v>
+        <v>-0.5538</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2704</v>
+        <v>-0.5401</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6996</v>
+        <v>0.4299</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4534</v>
+        <v>0.2443</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2462</v>
+        <v>0.1856</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,307 +1566,323 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.6024</v>
+        <v>-0.3142</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5689</v>
+        <v>-2.1572</v>
       </c>
       <c r="F14" t="n">
-        <v>9.0336</v>
+        <v>1.843</v>
       </c>
       <c r="G14" t="n">
-        <v>9.117399999999998</v>
+        <v>-1.5688</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.0658</v>
+        <v>-1.4879</v>
       </c>
       <c r="I14" t="n">
-        <v>16.1833</v>
+        <v>-0.0809</v>
       </c>
       <c r="J14" t="n">
-        <v>17.4561</v>
+        <v>-1.2095</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6142</v>
+        <v>-0.5897</v>
       </c>
       <c r="L14" t="n">
-        <v>14.8421</v>
+        <v>-0.6198</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.338699999999999</v>
+        <v>-0.3593</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.680199999999999</v>
+        <v>-0.8982</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3413</v>
+        <v>0.5389</v>
       </c>
       <c r="P14" t="n">
-        <v>2.930099999999999</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.7437</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6738</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>8.6257</v>
+        <v>0.6686</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9865</v>
+        <v>0.029</v>
       </c>
       <c r="U14" t="n">
-        <v>5.638999999999999</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>4.929499999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>6.87</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.9405</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4222</v>
+        <v>-0.199</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3454</v>
+        <v>-0.4164</v>
       </c>
       <c r="G15" t="n">
-        <v>2.512</v>
+        <v>-0.9791</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8361</v>
+        <v>-1.3976</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3241</v>
+        <v>0.4185</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6538</v>
+        <v>0.3243</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0097</v>
+        <v>-0.3646</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6441</v>
+        <v>0.6889</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1419</v>
+        <v>-1.3034</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1737</v>
+        <v>-1.033</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.9682</v>
+        <v>-0.2704</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0332</v>
+        <v>0.6996</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8995</v>
+        <v>0.4534</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1337</v>
+        <v>0.2462</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.7693</v>
+        <v>0.0549</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2138</v>
+        <v>-0.8194</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1358</v>
+        <v>-0.5645</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.078</v>
+        <v>-0.2549</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7072000000000001</v>
+        <v>-0.2027</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9366</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2294</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9819</v>
+        <v>-0.5322</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9414</v>
+        <v>-0.6536</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2747</v>
+        <v>0.3296</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0049</v>
+        <v>-0.0747</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2698</v>
+        <v>0.4043</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1396</v>
+        <v>0.0159</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.141</v>
+        <v>-0.0322</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0014</v>
+        <v>0.0481</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7871</v>
+        <v>25.60249999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0161</v>
+        <v>16.5689</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2291</v>
+        <v>9.0336</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1255</v>
+        <v>9.1175</v>
       </c>
       <c r="H17" t="n">
-        <v>0.142</v>
+        <v>-7.065799999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2675</v>
+        <v>16.1835</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1854</v>
+        <v>17.4562</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0819</v>
+        <v>2.6143</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2673</v>
+        <v>14.8421</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0599</v>
+        <v>-8.338699999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0601</v>
+        <v>-9.680199999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0002</v>
+        <v>1.3413</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>2.930099999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-10.7437</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>13.6738</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0523</v>
+        <v>8.625699999999998</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1693</v>
+        <v>2.9865</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2215</v>
+        <v>5.638999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.929500000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>6.87</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.9405</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5544</v>
+        <v>0.607</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7172</v>
+        <v>0.607</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1627</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6382</v>
+        <v>0.607</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3057</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9439</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6332</v>
+        <v>0.607</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0051</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3302</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1073</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2229</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6568</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5543</v>
+        <v>4.4222</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1025</v>
+        <v>-4.3454</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.229</v>
+        <v>2.512</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2845</v>
+        <v>2.8361</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9445</v>
+        <v>-0.3241</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2049</v>
+        <v>5.6538</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2049</v>
+        <v>3.0097</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6441</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0241</v>
+        <v>-3.1419</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0795</v>
+        <v>-0.1737</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>-2.9682</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4045</v>
+        <v>-1.0332</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3494</v>
+        <v>-0.8995</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0551</v>
+        <v>-0.1337</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.7693</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +2060,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7297</v>
+        <v>-0.2138</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7297</v>
+        <v>-0.1358</v>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>-0.078</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7139</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.768</v>
+        <v>0.9366</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0541</v>
+        <v>-0.2294</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0633</v>
+        <v>0.9819</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9414</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3494</v>
+        <v>-0.2747</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2144</v>
+        <v>-0.0049</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.135</v>
+        <v>-0.2698</v>
       </c>
       <c r="P20" t="n">
         <v>-0.7814</v>
@@ -2014,28 +2105,33 @@
         <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7208</v>
+        <v>-0.1396</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>-0.141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2367</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8369</v>
+        <v>-0.7871</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8496</v>
+        <v>-1.0161</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9873</v>
+        <v>0.2291</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2475</v>
+        <v>-1.1255</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3257</v>
+        <v>0.142</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5732</v>
+        <v>-1.2675</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6654</v>
+        <v>-1.1854</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6196</v>
+        <v>0.0819</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9542</v>
+        <v>-1.2673</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9129</v>
+        <v>0.0599</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>0.0601</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.619</v>
+        <v>-0.0002</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3391</v>
+        <v>-0.0523</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4835</v>
+        <v>0.1693</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1443</v>
+        <v>-0.2215</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1531</v>
+        <v>-1.5544</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.7172</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2272</v>
+        <v>0.1627</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1337</v>
+        <v>-0.6382</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8212</v>
+        <v>0.3057</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6875</v>
+        <v>-0.9439</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7793</v>
+        <v>-0.6332</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4672</v>
+        <v>0.0409</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6879</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3544</v>
+        <v>-0.0051</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.354</v>
+        <v>0.2648</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0004</v>
+        <v>-0.2698</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0194</v>
+        <v>-0.3302</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6657</v>
+        <v>-0.1073</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3536</v>
+        <v>-0.2229</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. COOPER SPACIR</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1113</v>
+        <v>-1.6568</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3483</v>
+        <v>-1.5543</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.763</v>
+        <v>-0.1025</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2391</v>
+        <v>-2.229</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6091</v>
+        <v>-1.2845</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8482</v>
+        <v>-0.9445</v>
       </c>
       <c r="J23" t="n">
-        <v>0.799</v>
+        <v>-1.2049</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7585</v>
+        <v>-1.2049</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.038</v>
+        <v>-1.0241</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1494</v>
+        <v>-0.0795</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8887</v>
+        <v>-0.9445</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1142</v>
+        <v>-0.4045</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1939</v>
+        <v>-0.3494</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.0551</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5358</v>
+        <v>-1.7297</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4771</v>
+        <v>-0.7297</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0587</v>
+        <v>-1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.193</v>
+        <v>0.7139</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2415</v>
+        <v>0.768</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0486</v>
+        <v>-0.0541</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5445</v>
+        <v>1.0633</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6247</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3516</v>
+        <v>-0.3494</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3832</v>
+        <v>-0.2144</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.9684</v>
+        <v>-0.135</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9534</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7753</v>
+        <v>-0.7208</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1148</v>
+        <v>-0.4842</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6605</v>
+        <v>-0.2367</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7012</v>
+        <v>-1.8369</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3455</v>
+        <v>-0.8496</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3557</v>
+        <v>-0.9873</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4444</v>
+        <v>-1.2475</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0893</v>
+        <v>2.3257</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.5337</v>
+        <v>-3.5732</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1766</v>
+        <v>0.6654</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7421</v>
+        <v>2.6196</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5655</v>
+        <v>-1.9542</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.621</v>
+        <v>-1.9129</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6528</v>
+        <v>-0.2939</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.9682</v>
+        <v>-1.619</v>
       </c>
       <c r="P25" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7842</v>
+        <v>-0.3391</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8459</v>
+        <v>-0.4835</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0617</v>
+        <v>0.1443</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2558,78 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.4226</v>
+        <v>-2.1531</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3564</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0663</v>
+        <v>-1.2272</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.186</v>
+        <v>-1.1337</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0824</v>
+        <v>-1.8212</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.1036</v>
+        <v>0.6875</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.7429</v>
+        <v>-0.7793</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.449</v>
+        <v>-1.4672</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2939</v>
+        <v>0.6879</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4431</v>
+        <v>-0.3544</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6334</v>
+        <v>-0.354</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8097</v>
+        <v>-0.0004</v>
       </c>
       <c r="P26" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9361</v>
+        <v>-1.0194</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5233</v>
+        <v>-0.6657</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4128</v>
+        <v>-0.3536</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8865</v>
+        <v>1.4959</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.7731</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. COOPER SPACIR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,68 +2641,401 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>-3.1113</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.3483</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.763</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.2391</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6091</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.8482</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.038</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.1494</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.8887</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1142</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1939</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E. ZUSTOVICH</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.5358</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.4771</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.0587</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.2415</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2.0486</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5445</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.6247</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-3.3516</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.3832</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.9684</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-1.7753</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.1148</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.6605</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M. DIALLO BADJI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-3.7012</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.3455</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.3557</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-2.4444</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.0893</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-3.5337</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.1766</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.7421</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.5655</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-3.621</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.6528</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-2.9682</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.7842</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.8459</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A. BENNASSAR ROSSELLO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-5.0296</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-2.9634</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-2.0663</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-3.793</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.0824</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-2.7106</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-2.3499</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.449</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-1.9009</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1.4431</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.6334</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.9361</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.5233</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.4128</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>play_by_play_2484220_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
         <v>-24.6259</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E31" t="n">
         <v>-9.0337</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F31" t="n">
         <v>-15.5923</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G31" t="n">
         <v>-9.1173</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H31" t="n">
         <v>7.065899999999999</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I31" t="n">
         <v>-16.1833</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J31" t="n">
         <v>8.338800000000001</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K31" t="n">
         <v>9.680100000000001</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L31" t="n">
         <v>-1.3412</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M31" t="n">
         <v>-17.4563</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N31" t="n">
         <v>-2.6143</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O31" t="n">
         <v>-14.8419</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P31" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q31" t="n">
         <v>-13.6739</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R31" t="n">
         <v>10.7437</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S31" t="n">
         <v>-7.648899999999999</v>
       </c>
-      <c r="T27" t="n">
-        <v>-5.639200000000001</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="T31" t="n">
+        <v>-5.6392</v>
+      </c>
+      <c r="U31" t="n">
         <v>-2.0097</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V31" t="n">
         <v>-4.9293</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W31" t="n">
         <v>1.9405</v>
       </c>
-      <c r="X27" t="n">
-        <v>-6.870100000000001</v>
-      </c>
+      <c r="X31" t="n">
+        <v>-6.870099999999999</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
